--- a/docs/FieldPro_UI_Test_Cases.xlsx
+++ b/docs/FieldPro_UI_Test_Cases.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,28 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -104,8 +124,33 @@
         <bgColor rgb="00E3E0F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -127,11 +172,25 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -162,6 +221,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,8 +604,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K279"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O279"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -541,6 +618,10 @@
     <col width="26" customWidth="1" min="9" max="9"/>
     <col width="46" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -599,6 +680,26 @@
           <t>Requirement Refs</t>
         </is>
       </c>
+      <c r="L1" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="M1" s="14" t="inlineStr">
+        <is>
+          <t>Actual Result / Notes</t>
+        </is>
+      </c>
+      <c r="N1" s="14" t="inlineStr">
+        <is>
+          <t>Executed At</t>
+        </is>
+      </c>
+      <c r="O1" s="14" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -655,6 +756,26 @@
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>PG-010</t>
+        </is>
+      </c>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M2" s="16" t="inlineStr">
+        <is>
+          <t>FieldPro Features Pricing Testimonials Contact Sign In Start Free Trial 🚀 Trust</t>
+        </is>
+      </c>
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:30.806Z</t>
+        </is>
+      </c>
+      <c r="O2" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -716,6 +837,26 @@
           <t>PG-011, FR-010</t>
         </is>
       </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>plans status=200 n=3; UI cards=15</t>
+        </is>
+      </c>
+      <c r="N3" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:32.329Z</t>
+        </is>
+      </c>
+      <c r="O3" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -775,6 +916,26 @@
           <t>PG-011, FR-010</t>
         </is>
       </c>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>requires killing API mid-session; not run on live prod</t>
+        </is>
+      </c>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:32.329Z</t>
+        </is>
+      </c>
+      <c r="O4" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -832,6 +993,26 @@
           <t>PG-012</t>
         </is>
       </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="inlineStr">
+        <is>
+          <t>https://field-worker-system.vercel.app/login</t>
+        </is>
+      </c>
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:33.731Z</t>
+        </is>
+      </c>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -887,6 +1068,26 @@
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>PG-013</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>signup CTAs=0</t>
+        </is>
+      </c>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:33.735Z</t>
+        </is>
+      </c>
+      <c r="O6" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -948,6 +1149,26 @@
           <t>PG-020, FR-011, FR-012, FR-020</t>
         </is>
       </c>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>UI https://field-worker-system.vercel.app/admin</t>
+        </is>
+      </c>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:37.074Z</t>
+        </is>
+      </c>
+      <c r="O7" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1007,6 +1228,26 @@
           <t>PG-020</t>
         </is>
       </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>password field present (toggle UI smoke)</t>
+        </is>
+      </c>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:34.087Z</t>
+        </is>
+      </c>
+      <c r="O8" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1066,6 +1307,26 @@
           <t>PG-021</t>
         </is>
       </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>remember-email persistence needs multi-session manual check</t>
+        </is>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:34.087Z</t>
+        </is>
+      </c>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1124,6 +1385,26 @@
           <t>PG-022</t>
         </is>
       </c>
+      <c r="L10" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>demo role chips present on login page (prod still shows them)</t>
+        </is>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:34.087Z</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1180,6 +1461,26 @@
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>FR-011</t>
+        </is>
+      </c>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>status=401</t>
+        </is>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:50.752Z</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -1241,6 +1542,26 @@
           <t>FR-011</t>
         </is>
       </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>status=401</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:50.931Z</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1299,6 +1620,26 @@
           <t>PG-023</t>
         </is>
       </c>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>requires stopping Render mid-test</t>
+        </is>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:34.087Z</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1356,6 +1697,26 @@
           <t>PG-024, FR-012</t>
         </is>
       </c>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>https://field-worker-system.vercel.app/super-admin</t>
+        </is>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:17.760Z</t>
+        </is>
+      </c>
+      <c r="O14" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1413,6 +1774,26 @@
           <t>PG-024, FR-012</t>
         </is>
       </c>
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>https://field-worker-system.vercel.app/worker</t>
+        </is>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:06.728Z</t>
+        </is>
+      </c>
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1468,6 +1849,26 @@
       <c r="K16" s="2" t="inlineStr">
         <is>
           <t>PG-024, FR-012, FR-022</t>
+        </is>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>office profile complete → /admin (onboarding not required)</t>
+        </is>
+      </c>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:37.074Z</t>
+        </is>
+      </c>
+      <c r="O16" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -1529,6 +1930,26 @@
           <t>PG-025, PG-026, FR-013</t>
         </is>
       </c>
+      <c r="L17" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant (signup creates company)</t>
+        </is>
+      </c>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O17" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1588,6 +2009,26 @@
           <t>PG-025, FR-014</t>
         </is>
       </c>
+      <c r="L18" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>status=400</t>
+        </is>
+      </c>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:51.112Z</t>
+        </is>
+      </c>
+      <c r="O18" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1647,6 +2088,26 @@
           <t>PG-026</t>
         </is>
       </c>
+      <c r="L19" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>status=409</t>
+        </is>
+      </c>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:51.377Z</t>
+        </is>
+      </c>
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1706,6 +2167,26 @@
           <t>PG-027, FR-015</t>
         </is>
       </c>
+      <c r="L20" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>existing=200 missing=200</t>
+        </is>
+      </c>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:52.162Z</t>
+        </is>
+      </c>
+      <c r="O20" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1765,6 +2246,26 @@
           <t>PG-030, PG-031, PG-033, FR-016</t>
         </is>
       </c>
+      <c r="L21" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>Needs valid reset token from email</t>
+        </is>
+      </c>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O21" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1823,6 +2324,26 @@
           <t>PG-032</t>
         </is>
       </c>
+      <c r="L22" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O22" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1881,6 +2402,26 @@
           <t>PG-032, FR-014</t>
         </is>
       </c>
+      <c r="L23" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>status=400</t>
+        </is>
+      </c>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:52.721Z</t>
+        </is>
+      </c>
+      <c r="O23" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1939,6 +2480,26 @@
           <t>PG-032</t>
         </is>
       </c>
+      <c r="L24" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>status=400</t>
+        </is>
+      </c>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:52.441Z</t>
+        </is>
+      </c>
+      <c r="O24" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1997,6 +2558,26 @@
           <t>FR-016, FR-017</t>
         </is>
       </c>
+      <c r="L25" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>Needs completed reset then session check</t>
+        </is>
+      </c>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2052,6 +2633,26 @@
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>PG-040, FR-021</t>
+        </is>
+      </c>
+      <c r="L26" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>Needs fresh invite token</t>
+        </is>
+      </c>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O26" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -2113,6 +2714,26 @@
           <t>PG-041, PG-042, PG-043, PG-044, FR-021, FR-141</t>
         </is>
       </c>
+      <c r="L27" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O27" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2171,6 +2792,26 @@
           <t>PG-043, FR-142, FR-230</t>
         </is>
       </c>
+      <c r="L28" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant (seat cap)</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O28" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2228,6 +2869,26 @@
           <t>PG-045, FR-021</t>
         </is>
       </c>
+      <c r="L29" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>status=400 (expired/invalid path)</t>
+        </is>
+      </c>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:53.063Z</t>
+        </is>
+      </c>
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2285,6 +2946,26 @@
           <t>PG-045</t>
         </is>
       </c>
+      <c r="L30" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>status=400 (used/invalid path)</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:53.063Z</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2343,6 +3024,26 @@
           <t>FR-038</t>
         </is>
       </c>
+      <c r="L31" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>RBAC invite-owner — needs non-owner session</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2398,6 +3099,26 @@
       <c r="K32" s="2" t="inlineStr">
         <is>
           <t>PG-050, PG-051</t>
+        </is>
+      </c>
+      <c r="L32" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>404 Oops! Page not found Return to Home</t>
+        </is>
+      </c>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:03.970Z</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -2459,6 +3180,26 @@
           <t>PG-060, FR-022</t>
         </is>
       </c>
+      <c r="L33" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>tenant already onboarded; cannot force without new owner</t>
+        </is>
+      </c>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:37.074Z</t>
+        </is>
+      </c>
+      <c r="O33" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2517,6 +3258,26 @@
           <t>PG-060</t>
         </is>
       </c>
+      <c r="L34" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N34" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O34" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2575,6 +3336,26 @@
           <t>PG-060, PG-064</t>
         </is>
       </c>
+      <c r="L35" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O35" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2633,6 +3414,26 @@
           <t>PG-061</t>
         </is>
       </c>
+      <c r="L36" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N36" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O36" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2691,6 +3492,26 @@
           <t>PG-062, FR-212</t>
         </is>
       </c>
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O37" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2749,6 +3570,26 @@
           <t>PG-066</t>
         </is>
       </c>
+      <c r="L38" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O38" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2807,6 +3648,26 @@
           <t>PG-063</t>
         </is>
       </c>
+      <c r="L39" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N39" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O39" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2865,6 +3726,26 @@
           <t>PG-065, FR-022</t>
         </is>
       </c>
+      <c r="L40" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N40" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O40" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2923,6 +3804,26 @@
           <t>PG-008, NFR-110</t>
         </is>
       </c>
+      <c r="L41" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N41" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O41" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2981,6 +3882,26 @@
           <t>PG-070, FR-060</t>
         </is>
       </c>
+      <c r="L42" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>status=200</t>
+        </is>
+      </c>
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:53.921Z</t>
+        </is>
+      </c>
+      <c r="O42" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3039,6 +3960,26 @@
           <t>PG-071</t>
         </is>
       </c>
+      <c r="L43" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>Dashboard payload returned (fields present for smoke)</t>
+        </is>
+      </c>
+      <c r="N43" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:53.922Z</t>
+        </is>
+      </c>
+      <c r="O43" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3097,6 +4038,26 @@
           <t>PG-072</t>
         </is>
       </c>
+      <c r="L44" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>Dashboard payload returned (fields present for smoke)</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:53.922Z</t>
+        </is>
+      </c>
+      <c r="O44" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3155,6 +4116,26 @@
           <t>PG-073</t>
         </is>
       </c>
+      <c r="L45" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>Dashboard payload returned (fields present for smoke)</t>
+        </is>
+      </c>
+      <c r="N45" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:53.922Z</t>
+        </is>
+      </c>
+      <c r="O45" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3211,6 +4192,26 @@
       <c r="K46" s="2" t="inlineStr">
         <is>
           <t>PG-074</t>
+        </is>
+      </c>
+      <c r="L46" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>Dashboard payload returned (fields present for smoke)</t>
+        </is>
+      </c>
+      <c r="N46" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:53.922Z</t>
+        </is>
+      </c>
+      <c r="O46" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -3272,6 +4273,26 @@
           <t>PG-075</t>
         </is>
       </c>
+      <c r="L47" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>Dashboard payload returned (fields present for smoke)</t>
+        </is>
+      </c>
+      <c r="N47" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:53.922Z</t>
+        </is>
+      </c>
+      <c r="O47" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3331,6 +4352,26 @@
           <t>PG-076</t>
         </is>
       </c>
+      <c r="L48" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>Dashboard payload returned (fields present for smoke)</t>
+        </is>
+      </c>
+      <c r="N48" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:53.922Z</t>
+        </is>
+      </c>
+      <c r="O48" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3389,6 +4430,26 @@
           <t>PG-077, PG-078</t>
         </is>
       </c>
+      <c r="L49" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>Dashboard payload returned (fields present for smoke)</t>
+        </is>
+      </c>
+      <c r="N49" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:53.922Z</t>
+        </is>
+      </c>
+      <c r="O49" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3447,6 +4508,26 @@
           <t>PG-080, FR-101, NFR-130</t>
         </is>
       </c>
+      <c r="L50" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>items=10; UI ok</t>
+        </is>
+      </c>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:39.924Z</t>
+        </is>
+      </c>
+      <c r="O50" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3505,6 +4586,26 @@
           <t>PG-081, FR-101</t>
         </is>
       </c>
+      <c r="L51" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>status=200</t>
+        </is>
+      </c>
+      <c r="N51" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:59.189Z</t>
+        </is>
+      </c>
+      <c r="O51" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3561,6 +4662,26 @@
       <c r="K52" s="2" t="inlineStr">
         <is>
           <t>PG-081, FR-101</t>
+        </is>
+      </c>
+      <c r="L52" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>list endpoint accepts query params (filter smoke)</t>
+        </is>
+      </c>
+      <c r="N52" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:59.189Z</t>
+        </is>
+      </c>
+      <c r="O52" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -3624,6 +4745,26 @@
           <t>PG-082, FR-082</t>
         </is>
       </c>
+      <c r="L53" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O53" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3680,6 +4821,26 @@
       <c r="K54" s="2" t="inlineStr">
         <is>
           <t>PG-083, FR-104</t>
+        </is>
+      </c>
+      <c r="L54" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O54" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -3744,6 +4905,26 @@
           <t>PG-084, PG-085, FR-090, FR-091, FR-093</t>
         </is>
       </c>
+      <c r="L55" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N55" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O55" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3802,6 +4983,26 @@
           <t>PG-085, FR-093</t>
         </is>
       </c>
+      <c r="L56" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N56" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O56" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3860,6 +5061,26 @@
           <t>PG-085, FR-094, CR-060</t>
         </is>
       </c>
+      <c r="L57" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N57" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O57" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3917,6 +5138,26 @@
           <t>FR-096, FR-231</t>
         </is>
       </c>
+      <c r="L58" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M58" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant (job cap)</t>
+        </is>
+      </c>
+      <c r="N58" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O58" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3975,6 +5216,26 @@
           <t>PG-517, FR-107</t>
         </is>
       </c>
+      <c r="L59" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M59" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O59" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4032,6 +5293,26 @@
           <t>PG-086</t>
         </is>
       </c>
+      <c r="L60" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M60" s="16" t="inlineStr">
+        <is>
+          <t>job 4d8b3fae-b3f7-49fa-bd08-a89ba75e7711</t>
+        </is>
+      </c>
+      <c r="N60" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:59.894Z</t>
+        </is>
+      </c>
+      <c r="O60" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4090,6 +5371,26 @@
           <t>PG-087, FR-102</t>
         </is>
       </c>
+      <c r="L61" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M61" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N61" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O61" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4148,6 +5449,26 @@
           <t>PG-088, FR-102</t>
         </is>
       </c>
+      <c r="L62" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M62" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O62" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4206,6 +5527,26 @@
           <t>PG-089</t>
         </is>
       </c>
+      <c r="L63" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M63" s="16" t="inlineStr">
+        <is>
+          <t>default list returns non-archived set</t>
+        </is>
+      </c>
+      <c r="N63" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:59.189Z</t>
+        </is>
+      </c>
+      <c r="O63" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4264,6 +5605,26 @@
           <t>PG-090, NFR-110</t>
         </is>
       </c>
+      <c r="L64" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M64" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N64" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O64" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4321,6 +5682,26 @@
           <t>PG-100</t>
         </is>
       </c>
+      <c r="L65" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M65" s="16" t="inlineStr">
+        <is>
+          <t>detail status=200</t>
+        </is>
+      </c>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:18:59.894Z</t>
+        </is>
+      </c>
+      <c r="O65" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4379,6 +5760,26 @@
           <t>PG-101, FR-263</t>
         </is>
       </c>
+      <c r="L66" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M66" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N66" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O66" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4437,6 +5838,26 @@
           <t>PG-102, FR-092, FR-097, FR-098, NFR-100</t>
         </is>
       </c>
+      <c r="L67" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M67" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N67" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O67" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4492,6 +5913,26 @@
       <c r="K68" s="2" t="inlineStr">
         <is>
           <t>PG-102, FR-098</t>
+        </is>
+      </c>
+      <c r="L68" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M68" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N68" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O68" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -4554,6 +5995,26 @@
           <t>PG-103, FR-094, CR-060</t>
         </is>
       </c>
+      <c r="L69" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M69" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N69" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O69" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4611,6 +6072,26 @@
           <t>PG-103, FR-095</t>
         </is>
       </c>
+      <c r="L70" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M70" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N70" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O70" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4669,6 +6150,26 @@
           <t>PG-104, FR-099</t>
         </is>
       </c>
+      <c r="L71" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M71" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N71" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O71" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4727,6 +6228,26 @@
           <t>PG-105, FR-099</t>
         </is>
       </c>
+      <c r="L72" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M72" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N72" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O72" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4783,6 +6304,26 @@
       <c r="K73" s="2" t="inlineStr">
         <is>
           <t>PG-106, FR-099, NFR-090</t>
+        </is>
+      </c>
+      <c r="L73" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M73" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N73" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O73" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -4844,6 +6385,26 @@
           <t>PG-107, FR-100, CR-030</t>
         </is>
       </c>
+      <c r="L74" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M74" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O74" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4901,6 +6462,26 @@
           <t>FR-100</t>
         </is>
       </c>
+      <c r="L75" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M75" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N75" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O75" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4957,6 +6538,26 @@
       <c r="K76" s="2" t="inlineStr">
         <is>
           <t>PG-108</t>
+        </is>
+      </c>
+      <c r="L76" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M76" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N76" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O76" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -5018,6 +6619,26 @@
           <t>PG-109, FR-103</t>
         </is>
       </c>
+      <c r="L77" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M77" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N77" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O77" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5076,6 +6697,26 @@
           <t>PG-110, FR-262</t>
         </is>
       </c>
+      <c r="L78" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M78" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N78" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O78" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5131,6 +6772,26 @@
       <c r="K79" s="2" t="inlineStr">
         <is>
           <t>PG-394, FR-053</t>
+        </is>
+      </c>
+      <c r="L79" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M79" s="16" t="inlineStr">
+        <is>
+          <t>status=404</t>
+        </is>
+      </c>
+      <c r="N79" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:19.304Z</t>
+        </is>
+      </c>
+      <c r="O79" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -5192,6 +6853,26 @@
           <t>PG-122, FR-110</t>
         </is>
       </c>
+      <c r="L80" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M80" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N80" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.168Z</t>
+        </is>
+      </c>
+      <c r="O80" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5251,6 +6932,26 @@
           <t>PG-120, FR-115</t>
         </is>
       </c>
+      <c r="L81" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M81" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N81" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:41.331Z</t>
+        </is>
+      </c>
+      <c r="O81" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5309,6 +7010,26 @@
           <t>PG-121, FR-115</t>
         </is>
       </c>
+      <c r="L82" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M82" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N82" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O82" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5367,6 +7088,26 @@
           <t>PG-124</t>
         </is>
       </c>
+      <c r="L83" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M83" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N83" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O83" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5422,6 +7163,26 @@
       <c r="K84" s="2" t="inlineStr">
         <is>
           <t>PG-130</t>
+        </is>
+      </c>
+      <c r="L84" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M84" s="16" t="inlineStr">
+        <is>
+          <t>status=200</t>
+        </is>
+      </c>
+      <c r="N84" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:01.953Z</t>
+        </is>
+      </c>
+      <c r="O84" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -5483,6 +7244,26 @@
           <t>PG-131</t>
         </is>
       </c>
+      <c r="L85" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M85" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N85" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O85" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5540,6 +7321,26 @@
           <t>PG-132, PG-133, FR-117, CR-070</t>
         </is>
       </c>
+      <c r="L86" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M86" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N86" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O86" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5597,6 +7398,26 @@
           <t>NFR-105, FR-117</t>
         </is>
       </c>
+      <c r="L87" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M87" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N87" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O87" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5654,6 +7475,26 @@
           <t>PG-132, FR-112</t>
         </is>
       </c>
+      <c r="L88" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M88" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N88" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O88" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5711,6 +7552,26 @@
           <t>PG-132, FR-111</t>
         </is>
       </c>
+      <c r="L89" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M89" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N89" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O89" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5769,6 +7630,26 @@
           <t>PG-134, FR-113, CR-040</t>
         </is>
       </c>
+      <c r="L90" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M90" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N90" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O90" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5826,6 +7707,26 @@
           <t>FR-113, CR-040</t>
         </is>
       </c>
+      <c r="L91" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M91" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N91" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O91" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5883,6 +7784,26 @@
           <t>FR-113, FR-096, FR-231</t>
         </is>
       </c>
+      <c r="L92" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M92" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N92" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O92" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5941,6 +7862,26 @@
           <t>PG-135, FR-114</t>
         </is>
       </c>
+      <c r="L93" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M93" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N93" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O93" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5999,6 +7940,26 @@
           <t>PG-136</t>
         </is>
       </c>
+      <c r="L94" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M94" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N94" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O94" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6057,6 +8018,26 @@
           <t>PG-140, PG-141, FR-120</t>
         </is>
       </c>
+      <c r="L95" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M95" s="16" t="inlineStr">
+        <is>
+          <t>calendar 200; UI ok</t>
+        </is>
+      </c>
+      <c r="N95" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:42.740Z</t>
+        </is>
+      </c>
+      <c r="O95" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6115,6 +8096,26 @@
           <t>PG-142</t>
         </is>
       </c>
+      <c r="L96" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M96" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N96" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O96" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6173,6 +8174,26 @@
           <t>PG-143</t>
         </is>
       </c>
+      <c r="L97" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M97" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N97" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O97" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6231,6 +8252,26 @@
           <t>PG-144, FR-037, FR-122</t>
         </is>
       </c>
+      <c r="L98" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M98" s="16" t="inlineStr">
+        <is>
+          <t>plan has calendar</t>
+        </is>
+      </c>
+      <c r="N98" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:12.368Z</t>
+        </is>
+      </c>
+      <c r="O98" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6289,6 +8330,26 @@
           <t>PG-150, PG-151, FR-121</t>
         </is>
       </c>
+      <c r="L99" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M99" s="16" t="inlineStr">
+        <is>
+          <t>dispatch 200; UI ok</t>
+        </is>
+      </c>
+      <c r="N99" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:44.124Z</t>
+        </is>
+      </c>
+      <c r="O99" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6347,6 +8408,26 @@
           <t>PG-152</t>
         </is>
       </c>
+      <c r="L100" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M100" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N100" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O100" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6402,6 +8483,26 @@
       <c r="K101" s="2" t="inlineStr">
         <is>
           <t>PG-153, FR-037, FR-122</t>
+        </is>
+      </c>
+      <c r="L101" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M101" s="16" t="inlineStr">
+        <is>
+          <t>plan has dispatch</t>
+        </is>
+      </c>
+      <c r="N101" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:13.000Z</t>
+        </is>
+      </c>
+      <c r="O101" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -6463,6 +8564,26 @@
           <t>PG-163, FR-070, FR-081</t>
         </is>
       </c>
+      <c r="L102" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M102" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N102" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O102" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6519,6 +8640,26 @@
       <c r="K103" s="2" t="inlineStr">
         <is>
           <t>FR-076</t>
+        </is>
+      </c>
+      <c r="L103" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M103" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N103" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O103" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -6578,6 +8719,26 @@
       <c r="K104" s="2" t="inlineStr">
         <is>
           <t>PG-160, PG-161, FR-077</t>
+        </is>
+      </c>
+      <c r="L104" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M104" s="16" t="inlineStr">
+        <is>
+          <t>items=10; UI ok</t>
+        </is>
+      </c>
+      <c r="N104" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:45.527Z</t>
+        </is>
+      </c>
+      <c r="O104" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -6640,6 +8801,26 @@
           <t>PG-162, FR-082</t>
         </is>
       </c>
+      <c r="L105" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M105" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N105" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O105" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6699,6 +8880,26 @@
           <t>PG-165, FR-078</t>
         </is>
       </c>
+      <c r="L106" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M106" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N106" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O106" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6757,6 +8958,26 @@
           <t>PG-165, FR-083</t>
         </is>
       </c>
+      <c r="L107" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M107" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N107" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O107" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6813,6 +9034,26 @@
       <c r="K108" s="2" t="inlineStr">
         <is>
           <t>PG-166, FR-080</t>
+        </is>
+      </c>
+      <c r="L108" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M108" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N108" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O108" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -6875,6 +9116,26 @@
           <t>PG-167, FR-075</t>
         </is>
       </c>
+      <c r="L109" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M109" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N109" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O109" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6933,6 +9194,26 @@
           <t>PG-167, FR-075</t>
         </is>
       </c>
+      <c r="L110" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M110" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N110" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O110" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6991,6 +9272,26 @@
           <t>PG-168, FR-075</t>
         </is>
       </c>
+      <c r="L111" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M111" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N111" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O111" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7048,6 +9349,26 @@
           <t>FR-079</t>
         </is>
       </c>
+      <c r="L112" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M112" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N112" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O112" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7106,6 +9427,26 @@
           <t>FR-079, PG-188</t>
         </is>
       </c>
+      <c r="L113" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M113" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N113" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O113" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7164,6 +9505,26 @@
           <t>PG-003, FR-084, FR-260</t>
         </is>
       </c>
+      <c r="L114" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M114" s="16" t="inlineStr">
+        <is>
+          <t>status=200</t>
+        </is>
+      </c>
+      <c r="N114" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:16.407Z</t>
+        </is>
+      </c>
+      <c r="O114" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7222,6 +9583,26 @@
           <t>PG-169, FR-085</t>
         </is>
       </c>
+      <c r="L115" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M115" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N115" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O115" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -7277,6 +9658,26 @@
       <c r="K116" s="2" t="inlineStr">
         <is>
           <t>PG-180</t>
+        </is>
+      </c>
+      <c r="L116" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M116" s="16" t="inlineStr">
+        <is>
+          <t>status=200</t>
+        </is>
+      </c>
+      <c r="N116" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:04.796Z</t>
+        </is>
+      </c>
+      <c r="O116" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -7336,6 +9737,26 @@
       <c r="K117" s="2" t="inlineStr">
         <is>
           <t>PG-181, PG-189, NFR-110</t>
+        </is>
+      </c>
+      <c r="L117" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M117" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N117" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O117" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -7398,6 +9819,26 @@
           <t>PG-182, FR-071</t>
         </is>
       </c>
+      <c r="L118" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M118" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N118" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O118" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7458,6 +9899,26 @@
           <t>PG-183, FR-071</t>
         </is>
       </c>
+      <c r="L119" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M119" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N119" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O119" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7514,6 +9975,26 @@
       <c r="K120" s="2" t="inlineStr">
         <is>
           <t>PG-184, FR-072</t>
+        </is>
+      </c>
+      <c r="L120" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M120" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N120" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O120" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -7575,6 +10056,26 @@
           <t>PG-185, FR-073</t>
         </is>
       </c>
+      <c r="L121" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M121" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N121" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O121" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7632,6 +10133,26 @@
           <t>PG-185</t>
         </is>
       </c>
+      <c r="L122" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M122" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N122" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O122" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7689,6 +10210,26 @@
           <t>PG-186, FR-074</t>
         </is>
       </c>
+      <c r="L123" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M123" s="16" t="inlineStr">
+        <is>
+          <t>profile payload includes related collections when present</t>
+        </is>
+      </c>
+      <c r="N123" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:04.796Z</t>
+        </is>
+      </c>
+      <c r="O123" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7746,6 +10287,26 @@
           <t>PG-187, FR-074</t>
         </is>
       </c>
+      <c r="L124" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M124" s="16" t="inlineStr">
+        <is>
+          <t>activity/related available via profile APIs</t>
+        </is>
+      </c>
+      <c r="N124" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:04.796Z</t>
+        </is>
+      </c>
+      <c r="O124" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7802,6 +10363,26 @@
       <c r="K125" s="2" t="inlineStr">
         <is>
           <t>PG-189, FR-262, FR-263</t>
+        </is>
+      </c>
+      <c r="L125" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M125" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N125" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O125" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -7864,6 +10445,26 @@
           <t>PG-201, FR-140, FR-141</t>
         </is>
       </c>
+      <c r="L126" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M126" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N126" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O126" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7919,6 +10520,26 @@
       <c r="K127" s="2" t="inlineStr">
         <is>
           <t>PG-205, FR-142, FR-230</t>
+        </is>
+      </c>
+      <c r="L127" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M127" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N127" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O127" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -7980,6 +10601,26 @@
           <t>PG-202, FR-143</t>
         </is>
       </c>
+      <c r="L128" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M128" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N128" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O128" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -8038,6 +10679,26 @@
           <t>PG-203, FR-143</t>
         </is>
       </c>
+      <c r="L129" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M129" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N129" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O129" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8096,6 +10757,26 @@
           <t>PG-204, FR-143</t>
         </is>
       </c>
+      <c r="L130" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M130" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N130" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O130" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -8153,6 +10834,26 @@
           <t>PG-205, FR-142</t>
         </is>
       </c>
+      <c r="L131" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M131" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N131" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O131" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -8211,6 +10912,26 @@
           <t>PG-206, FR-144</t>
         </is>
       </c>
+      <c r="L132" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M132" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N132" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O132" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8266,6 +10987,26 @@
       <c r="K133" s="2" t="inlineStr">
         <is>
           <t>FR-145</t>
+        </is>
+      </c>
+      <c r="L133" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M133" s="16" t="inlineStr">
+        <is>
+          <t>search includes workers when permitted</t>
+        </is>
+      </c>
+      <c r="N133" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:16.407Z</t>
+        </is>
+      </c>
+      <c r="O133" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -8327,6 +11068,26 @@
           <t>PG-211, FR-151, FR-152</t>
         </is>
       </c>
+      <c r="L134" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M134" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N134" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O134" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8384,6 +11145,26 @@
           <t>FR-151</t>
         </is>
       </c>
+      <c r="L135" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M135" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N135" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O135" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8442,6 +11223,26 @@
           <t>PG-212, FR-152</t>
         </is>
       </c>
+      <c r="L136" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M136" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N136" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O136" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8499,6 +11300,26 @@
           <t>PG-214, FR-153</t>
         </is>
       </c>
+      <c r="L137" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M137" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N137" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O137" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8557,6 +11378,26 @@
           <t>PG-213</t>
         </is>
       </c>
+      <c r="L138" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M138" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N138" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O138" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -8614,6 +11455,26 @@
           <t>PG-215, FR-037, FR-150</t>
         </is>
       </c>
+      <c r="L139" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M139" s="16" t="inlineStr">
+        <is>
+          <t>inventory accessible (plan has feature or allowed)</t>
+        </is>
+      </c>
+      <c r="N139" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:06.828Z</t>
+        </is>
+      </c>
+      <c r="O139" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8669,6 +11530,26 @@
       <c r="K140" s="2" t="inlineStr">
         <is>
           <t>PG-215, FR-154</t>
+        </is>
+      </c>
+      <c r="L140" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M140" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N140" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O140" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -8730,6 +11611,26 @@
           <t>PG-220, PG-221, FR-134, FR-135</t>
         </is>
       </c>
+      <c r="L141" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M141" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N141" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:49.810Z</t>
+        </is>
+      </c>
+      <c r="O141" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8788,6 +11689,26 @@
           <t>PG-222, PG-223, FR-132, FR-136</t>
         </is>
       </c>
+      <c r="L142" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M142" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N142" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O142" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8845,6 +11766,26 @@
           <t>PG-224, FR-132</t>
         </is>
       </c>
+      <c r="L143" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M143" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N143" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O143" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -8903,6 +11844,26 @@
           <t>FR-133</t>
         </is>
       </c>
+      <c r="L144" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M144" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N144" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O144" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -8960,6 +11921,26 @@
           <t>PG-225</t>
         </is>
       </c>
+      <c r="L145" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M145" s="16" t="inlineStr">
+        <is>
+          <t>status=200</t>
+        </is>
+      </c>
+      <c r="N145" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:08.394Z</t>
+        </is>
+      </c>
+      <c r="O145" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -9017,6 +11998,26 @@
           <t>FR-135</t>
         </is>
       </c>
+      <c r="L146" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M146" s="16" t="inlineStr">
+        <is>
+          <t>search endpoint aggregates invoices/customers</t>
+        </is>
+      </c>
+      <c r="N146" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:16.407Z</t>
+        </is>
+      </c>
+      <c r="O146" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -9072,6 +12073,26 @@
       <c r="K147" s="2" t="inlineStr">
         <is>
           <t>PG-230, FR-170</t>
+        </is>
+      </c>
+      <c r="L147" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M147" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N147" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:51.245Z</t>
+        </is>
+      </c>
+      <c r="O147" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -9133,6 +12154,26 @@
           <t>PG-231, FR-170</t>
         </is>
       </c>
+      <c r="L148" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M148" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N148" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O148" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9192,6 +12233,26 @@
           <t>PG-232, FR-170, FR-172</t>
         </is>
       </c>
+      <c r="L149" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M149" s="16" t="inlineStr">
+        <is>
+          <t>Needs live Socket.io message round-trip</t>
+        </is>
+      </c>
+      <c r="N149" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O149" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9250,6 +12311,26 @@
           <t>PG-233, FR-170</t>
         </is>
       </c>
+      <c r="L150" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M150" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N150" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O150" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9305,6 +12386,26 @@
       <c r="K151" s="2" t="inlineStr">
         <is>
           <t>PG-410, PG-411, FR-171</t>
+        </is>
+      </c>
+      <c r="L151" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M151" s="16" t="inlineStr">
+        <is>
+          <t>UI /worker/chat</t>
+        </is>
+      </c>
+      <c r="N151" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:12.388Z</t>
+        </is>
+      </c>
+      <c r="O151" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -9366,6 +12467,26 @@
           <t>PG-240, PG-241, FR-160, FR-161</t>
         </is>
       </c>
+      <c r="L152" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M152" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N152" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:52.671Z</t>
+        </is>
+      </c>
+      <c r="O152" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9422,6 +12543,26 @@
       <c r="K153" s="2" t="inlineStr">
         <is>
           <t>PG-242, FR-161</t>
+        </is>
+      </c>
+      <c r="L153" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M153" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N153" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O153" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -9483,6 +12624,26 @@
           <t>PG-243, FR-161</t>
         </is>
       </c>
+      <c r="L154" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M154" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N154" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O154" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -9542,6 +12703,26 @@
           <t>PG-244, FR-162</t>
         </is>
       </c>
+      <c r="L155" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M155" s="16" t="inlineStr">
+        <is>
+          <t>Twilio credentials/send</t>
+        </is>
+      </c>
+      <c r="N155" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O155" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -9599,6 +12780,26 @@
           <t>PG-244, PG-245, FR-164</t>
         </is>
       </c>
+      <c r="L156" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M156" s="16" t="inlineStr">
+        <is>
+          <t>Twilio not configured graceful fail — manual</t>
+        </is>
+      </c>
+      <c r="N156" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O156" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -9655,6 +12856,26 @@
       <c r="K157" s="2" t="inlineStr">
         <is>
           <t>PG-247, FR-163</t>
+        </is>
+      </c>
+      <c r="L157" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M157" s="16" t="inlineStr">
+        <is>
+          <t>Inbound webhook — needs Twilio callback</t>
+        </is>
+      </c>
+      <c r="N157" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O157" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -9714,6 +12935,26 @@
       <c r="K158" s="2" t="inlineStr">
         <is>
           <t>PG-246, FR-165, CR-070</t>
+        </is>
+      </c>
+      <c r="L158" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M158" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N158" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O158" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -9776,6 +13017,26 @@
           <t>PG-250, PG-251, PG-252, FR-180</t>
         </is>
       </c>
+      <c r="L159" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M159" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N159" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O159" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -9833,6 +13094,26 @@
           <t>FR-180</t>
         </is>
       </c>
+      <c r="L160" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M160" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N160" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O160" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -9890,6 +13171,26 @@
           <t>PG-253, FR-180</t>
         </is>
       </c>
+      <c r="L161" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M161" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N161" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O161" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -9948,6 +13249,26 @@
           <t>PG-254, FR-180</t>
         </is>
       </c>
+      <c r="L162" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M162" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N162" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.169Z</t>
+        </is>
+      </c>
+      <c r="O162" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -10003,6 +13324,26 @@
       <c r="K163" s="2" t="inlineStr">
         <is>
           <t>PG-181 (search), FR-181</t>
+        </is>
+      </c>
+      <c r="L163" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M163" s="16" t="inlineStr">
+        <is>
+          <t>search endpoint available for documents</t>
+        </is>
+      </c>
+      <c r="N163" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:16.407Z</t>
+        </is>
+      </c>
+      <c r="O163" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -10064,6 +13405,26 @@
           <t>PG-261, FR-182</t>
         </is>
       </c>
+      <c r="L164" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M164" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N164" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O164" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -10120,6 +13481,26 @@
       <c r="K165" s="2" t="inlineStr">
         <is>
           <t>PG-262, FR-182</t>
+        </is>
+      </c>
+      <c r="L165" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M165" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N165" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O165" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -10181,6 +13562,26 @@
           <t>PG-263</t>
         </is>
       </c>
+      <c r="L166" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M166" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N166" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O166" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -10236,6 +13637,26 @@
       <c r="K167" s="2" t="inlineStr">
         <is>
           <t>PG-264, FR-182</t>
+        </is>
+      </c>
+      <c r="L167" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M167" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N167" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O167" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -10298,6 +13719,26 @@
           <t>PG-271, PG-272, PG-273, FR-183</t>
         </is>
       </c>
+      <c r="L168" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M168" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N168" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O168" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -10357,6 +13798,26 @@
           <t>PG-271</t>
         </is>
       </c>
+      <c r="L169" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M169" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N169" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O169" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -10414,6 +13875,26 @@
           <t>PG-274, FR-183</t>
         </is>
       </c>
+      <c r="L170" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M170" s="16" t="inlineStr">
+        <is>
+          <t>Assert platform templates read-only — manual</t>
+        </is>
+      </c>
+      <c r="N170" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O170" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -10471,6 +13952,26 @@
           <t>PG-275, FR-183</t>
         </is>
       </c>
+      <c r="L171" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M171" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N171" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O171" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -10528,6 +14029,26 @@
           <t>PG-280, PG-281, PG-282, FR-190</t>
         </is>
       </c>
+      <c r="L172" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M172" s="16" t="inlineStr">
+        <is>
+          <t>reports payload 200; UI ok</t>
+        </is>
+      </c>
+      <c r="N172" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:58.398Z</t>
+        </is>
+      </c>
+      <c r="O172" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -10583,6 +14104,26 @@
       <c r="K173" s="2" t="inlineStr">
         <is>
           <t>PG-283, FR-037, FR-190</t>
+        </is>
+      </c>
+      <c r="L173" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M173" s="16" t="inlineStr">
+        <is>
+          <t>plan includes reports or allowed</t>
+        </is>
+      </c>
+      <c r="N173" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:11.784Z</t>
+        </is>
+      </c>
+      <c r="O173" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -10644,6 +14185,26 @@
           <t>PG-290, PG-291, PG-293, FR-210</t>
         </is>
       </c>
+      <c r="L174" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M174" s="16" t="inlineStr">
+        <is>
+          <t>UI /admin/settings → https://field-worker-system.vercel.app/admin/settings FieldPro Mitesoft Dashboard Jobs Estimates Calendar Dispatch Customers Workers I</t>
+        </is>
+      </c>
+      <c r="N174" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:59.792Z</t>
+        </is>
+      </c>
+      <c r="O174" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -10702,6 +14263,26 @@
           <t>PG-292, FR-210</t>
         </is>
       </c>
+      <c r="L175" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M175" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N175" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O175" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -10759,6 +14340,26 @@
           <t>PG-300</t>
         </is>
       </c>
+      <c r="L176" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M176" s="16" t="inlineStr">
+        <is>
+          <t>status=200</t>
+        </is>
+      </c>
+      <c r="N176" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:14.690Z</t>
+        </is>
+      </c>
+      <c r="O176" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -10816,6 +14417,26 @@
           <t>PG-301, FR-038</t>
         </is>
       </c>
+      <c r="L177" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M177" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N177" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O177" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -10873,6 +14494,26 @@
           <t>PG-301, FR-038</t>
         </is>
       </c>
+      <c r="L178" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M178" s="16" t="inlineStr">
+        <is>
+          <t>Needs non-owner admin session</t>
+        </is>
+      </c>
+      <c r="N178" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O178" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -10928,6 +14569,26 @@
       <c r="K179" s="2" t="inlineStr">
         <is>
           <t>PG-302, FR-142, FR-230</t>
+        </is>
+      </c>
+      <c r="L179" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M179" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N179" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O179" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -10989,6 +14650,26 @@
           <t>PG-303, FR-036</t>
         </is>
       </c>
+      <c r="L180" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M180" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N180" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O180" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -11044,6 +14725,26 @@
       <c r="K181" s="2" t="inlineStr">
         <is>
           <t>PG-304</t>
+        </is>
+      </c>
+      <c r="L181" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M181" s="16" t="inlineStr">
+        <is>
+          <t>members/invites payload available</t>
+        </is>
+      </c>
+      <c r="N181" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:14.690Z</t>
+        </is>
+      </c>
+      <c r="O181" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -11105,6 +14806,26 @@
           <t>PG-305, FR-039, CR-050</t>
         </is>
       </c>
+      <c r="L182" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M182" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N182" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O182" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -11162,6 +14883,26 @@
       <c r="K183" s="2" t="inlineStr">
         <is>
           <t>PG-310, PG-311, FR-212, NFR-030</t>
+        </is>
+      </c>
+      <c r="L183" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M183" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N183" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O183" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -11224,6 +14965,26 @@
           <t>PG-311</t>
         </is>
       </c>
+      <c r="L184" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M184" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N184" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O184" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -11282,6 +15043,26 @@
           <t>PG-312, PG-521</t>
         </is>
       </c>
+      <c r="L185" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M185" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N185" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O185" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -11339,6 +15120,26 @@
           <t>PG-314, FR-032</t>
         </is>
       </c>
+      <c r="L186" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M186" s="16" t="inlineStr">
+        <is>
+          <t>Needs admin without smtp permission</t>
+        </is>
+      </c>
+      <c r="N186" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O186" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -11397,6 +15198,26 @@
           <t>PG-314, FR-256</t>
         </is>
       </c>
+      <c r="L187" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M187" s="16" t="inlineStr">
+        <is>
+          <t>Isolation check — manual/code review</t>
+        </is>
+      </c>
+      <c r="N187" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O187" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -11454,6 +15275,26 @@
           <t>PG-320</t>
         </is>
       </c>
+      <c r="L188" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M188" s="16" t="inlineStr">
+        <is>
+          <t>Twilio guidance visible under settings/comms when opened</t>
+        </is>
+      </c>
+      <c r="N188" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:02.579Z</t>
+        </is>
+      </c>
+      <c r="O188" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -11511,6 +15352,26 @@
           <t>PG-321</t>
         </is>
       </c>
+      <c r="L189" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M189" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N189" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O189" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -11568,6 +15429,26 @@
           <t>PG-330, FR-213</t>
         </is>
       </c>
+      <c r="L190" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M190" s="16" t="inlineStr">
+        <is>
+          <t>GET /billing → 200</t>
+        </is>
+      </c>
+      <c r="N190" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:24:55.623122+00:00</t>
+        </is>
+      </c>
+      <c r="O190" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -11626,6 +15507,26 @@
           <t>PG-331, FR-220</t>
         </is>
       </c>
+      <c r="L191" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M191" s="16" t="inlineStr">
+        <is>
+          <t>Stripe Checkout — mutating billing</t>
+        </is>
+      </c>
+      <c r="N191" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O191" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -11684,6 +15585,26 @@
           <t>PG-334, FR-221</t>
         </is>
       </c>
+      <c r="L192" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M192" s="16" t="inlineStr">
+        <is>
+          <t>Depends on Stripe key presence — verify in UI</t>
+        </is>
+      </c>
+      <c r="N192" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O192" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -11741,6 +15662,26 @@
           <t>PG-332</t>
         </is>
       </c>
+      <c r="L193" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M193" s="16" t="inlineStr">
+        <is>
+          <t>Stripe portal — mutating</t>
+        </is>
+      </c>
+      <c r="N193" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O193" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -11799,6 +15740,26 @@
           <t>PG-333, FR-213</t>
         </is>
       </c>
+      <c r="L194" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M194" s="16" t="inlineStr">
+        <is>
+          <t>SaaS invoices list — verify in billing UI</t>
+        </is>
+      </c>
+      <c r="N194" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O194" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -11856,6 +15817,26 @@
           <t>FR-224</t>
         </is>
       </c>
+      <c r="L195" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M195" s="16" t="inlineStr">
+        <is>
+          <t>Checkout trial days — Stripe</t>
+        </is>
+      </c>
+      <c r="N195" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O195" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -11912,6 +15893,26 @@
       <c r="K196" s="2" t="inlineStr">
         <is>
           <t>PG-340, PG-341, FR-214</t>
+        </is>
+      </c>
+      <c r="L196" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M196" s="16" t="inlineStr">
+        <is>
+          <t>notification prefs reachable via profile/settings</t>
+        </is>
+      </c>
+      <c r="N196" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:02.579Z</t>
+        </is>
+      </c>
+      <c r="O196" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -11973,6 +15974,26 @@
           <t>PG-350</t>
         </is>
       </c>
+      <c r="L197" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M197" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N197" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:01.184Z</t>
+        </is>
+      </c>
+      <c r="O197" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -12032,6 +16053,26 @@
           <t>PG-351</t>
         </is>
       </c>
+      <c r="L198" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M198" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N198" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O198" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -12087,6 +16128,26 @@
       <c r="K199" s="2" t="inlineStr">
         <is>
           <t>PG-352</t>
+        </is>
+      </c>
+      <c r="L199" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M199" s="16" t="inlineStr">
+        <is>
+          <t>role=owner</t>
+        </is>
+      </c>
+      <c r="N199" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:15.481Z</t>
+        </is>
+      </c>
+      <c r="O199" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -12149,6 +16210,26 @@
           <t>PG-360, PG-361, PG-362, FR-200</t>
         </is>
       </c>
+      <c r="L200" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M200" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N200" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:02.578Z</t>
+        </is>
+      </c>
+      <c r="O200" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -12207,6 +16288,26 @@
           <t>PG-004, FR-201</t>
         </is>
       </c>
+      <c r="L201" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M201" s="16" t="inlineStr">
+        <is>
+          <t>notifications API reachable for bell</t>
+        </is>
+      </c>
+      <c r="N201" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:15.954Z</t>
+        </is>
+      </c>
+      <c r="O201" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -12265,6 +16366,26 @@
           <t>PG-370, FR-240</t>
         </is>
       </c>
+      <c r="L202" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M202" s="16" t="inlineStr">
+        <is>
+          <t>assigned jobs available for dashboard; UI ok</t>
+        </is>
+      </c>
+      <c r="N202" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:08.143Z</t>
+        </is>
+      </c>
+      <c r="O202" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -12322,6 +16443,26 @@
           <t>PG-371</t>
         </is>
       </c>
+      <c r="L203" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M203" s="16" t="inlineStr">
+        <is>
+          <t>worker dashboard links to jobs/schedule/chat</t>
+        </is>
+      </c>
+      <c r="N203" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:13.777Z</t>
+        </is>
+      </c>
+      <c r="O203" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -12379,6 +16520,26 @@
           <t>PG-380, FR-053, FR-241</t>
         </is>
       </c>
+      <c r="L204" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M204" s="16" t="inlineStr">
+        <is>
+          <t>items=2; UI ok</t>
+        </is>
+      </c>
+      <c r="N204" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:09.554Z</t>
+        </is>
+      </c>
+      <c r="O204" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -12436,6 +16597,26 @@
           <t>PG-382</t>
         </is>
       </c>
+      <c r="L205" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M205" s="16" t="inlineStr">
+        <is>
+          <t>worker can query own jobs list</t>
+        </is>
+      </c>
+      <c r="N205" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:18.091Z</t>
+        </is>
+      </c>
+      <c r="O205" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -12491,6 +16672,26 @@
       <c r="K206" s="2" t="inlineStr">
         <is>
           <t>PG-390</t>
+        </is>
+      </c>
+      <c r="L206" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M206" s="16" t="inlineStr">
+        <is>
+          <t>status=200</t>
+        </is>
+      </c>
+      <c r="N206" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:18.849Z</t>
+        </is>
+      </c>
+      <c r="O206" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -12552,6 +16753,26 @@
           <t>PG-391, FR-097, FR-241</t>
         </is>
       </c>
+      <c r="L207" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M207" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N207" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O207" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -12610,6 +16831,26 @@
           <t>PG-392, PG-393, FR-241</t>
         </is>
       </c>
+      <c r="L208" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M208" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N208" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O208" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -12667,6 +16908,26 @@
           <t>PG-394, FR-053</t>
         </is>
       </c>
+      <c r="L209" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M209" s="16" t="inlineStr">
+        <is>
+          <t>status=404</t>
+        </is>
+      </c>
+      <c r="N209" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:19.304Z</t>
+        </is>
+      </c>
+      <c r="O209" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -12724,6 +16985,26 @@
           <t>PG-400, FR-242</t>
         </is>
       </c>
+      <c r="L210" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M210" s="16" t="inlineStr">
+        <is>
+          <t>schedule fed from assigned jobs; UI ok</t>
+        </is>
+      </c>
+      <c r="N210" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:10.987Z</t>
+        </is>
+      </c>
+      <c r="O210" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -12779,6 +17060,26 @@
       <c r="K211" s="2" t="inlineStr">
         <is>
           <t>PG-401</t>
+        </is>
+      </c>
+      <c r="L211" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M211" s="16" t="inlineStr">
+        <is>
+          <t>schedule page loads (open job from schedule = manual deep check)</t>
+        </is>
+      </c>
+      <c r="N211" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:13.777Z</t>
+        </is>
+      </c>
+      <c r="O211" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -12840,6 +17141,26 @@
           <t>PG-420</t>
         </is>
       </c>
+      <c r="L212" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M212" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N212" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:13.777Z</t>
+        </is>
+      </c>
+      <c r="O212" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -12898,6 +17219,26 @@
           <t>PG-421</t>
         </is>
       </c>
+      <c r="L213" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M213" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N213" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O213" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -12955,6 +17296,26 @@
           <t>FR-244</t>
         </is>
       </c>
+      <c r="L214" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M214" s="16" t="inlineStr">
+        <is>
+          <t>url=https://field-worker-system.vercel.app/login</t>
+        </is>
+      </c>
+      <c r="N214" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:15.172Z</t>
+        </is>
+      </c>
+      <c r="O214" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -13013,6 +17374,26 @@
           <t>PG-430, PG-431, PG-432, FR-251</t>
         </is>
       </c>
+      <c r="L215" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M215" s="16" t="inlineStr">
+        <is>
+          <t>companies 200; UI ok</t>
+        </is>
+      </c>
+      <c r="N215" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:19.157Z</t>
+        </is>
+      </c>
+      <c r="O215" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -13068,6 +17449,26 @@
       <c r="K216" s="2" t="inlineStr">
         <is>
           <t>PG-440</t>
+        </is>
+      </c>
+      <c r="L216" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M216" s="16" t="inlineStr">
+        <is>
+          <t>items=5; UI ok</t>
+        </is>
+      </c>
+      <c r="N216" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:20.539Z</t>
+        </is>
+      </c>
+      <c r="O216" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -13130,6 +17531,26 @@
           <t>PG-441, FR-252, CR-020</t>
         </is>
       </c>
+      <c r="L217" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M217" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N217" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O217" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -13190,6 +17611,26 @@
           <t>PG-442, FR-054</t>
         </is>
       </c>
+      <c r="L218" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M218" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N218" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O218" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -13248,6 +17689,26 @@
           <t>PG-443</t>
         </is>
       </c>
+      <c r="L219" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M219" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N219" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O219" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -13305,6 +17766,26 @@
           <t>PG-444</t>
         </is>
       </c>
+      <c r="L220" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M220" s="16" t="inlineStr">
+        <is>
+          <t>status=200</t>
+        </is>
+      </c>
+      <c r="N220" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:21.261Z</t>
+        </is>
+      </c>
+      <c r="O220" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -13362,6 +17843,26 @@
           <t>PG-450</t>
         </is>
       </c>
+      <c r="L221" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M221" s="16" t="inlineStr">
+        <is>
+          <t>status=200</t>
+        </is>
+      </c>
+      <c r="N221" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:21.261Z</t>
+        </is>
+      </c>
+      <c r="O221" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -13417,6 +17918,26 @@
       <c r="K222" s="2" t="inlineStr">
         <is>
           <t>PG-451</t>
+        </is>
+      </c>
+      <c r="L222" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M222" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N222" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O222" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -13478,6 +17999,26 @@
           <t>PG-452, FR-253</t>
         </is>
       </c>
+      <c r="L223" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M223" s="16" t="inlineStr">
+        <is>
+          <t>Impersonation — manual SA flow</t>
+        </is>
+      </c>
+      <c r="N223" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O223" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -13535,6 +18076,26 @@
           <t>PG-453, PG-007, FR-253</t>
         </is>
       </c>
+      <c r="L224" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M224" s="16" t="inlineStr">
+        <is>
+          <t>Stop impersonation — manual</t>
+        </is>
+      </c>
+      <c r="N224" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O224" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -13593,6 +18154,26 @@
           <t>FR-018</t>
         </is>
       </c>
+      <c r="L225" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M225" s="16" t="inlineStr">
+        <is>
+          <t>Impersonation refresh behavior — manual</t>
+        </is>
+      </c>
+      <c r="N225" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O225" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -13650,6 +18231,26 @@
           <t>FR-001</t>
         </is>
       </c>
+      <c r="L226" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M226" s="16" t="inlineStr">
+        <is>
+          <t>SA jobs status=403</t>
+        </is>
+      </c>
+      <c r="N226" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.507Z</t>
+        </is>
+      </c>
+      <c r="O226" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -13705,6 +18306,26 @@
       <c r="K227" s="2" t="inlineStr">
         <is>
           <t>PG-460</t>
+        </is>
+      </c>
+      <c r="L227" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M227" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N227" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:21.935Z</t>
+        </is>
+      </c>
+      <c r="O227" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -13768,6 +18389,26 @@
           <t>PG-461, PG-462, PG-463, FR-254</t>
         </is>
       </c>
+      <c r="L228" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M228" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N228" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O228" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -13826,6 +18467,26 @@
           <t>FR-232, §9 Out of scope</t>
         </is>
       </c>
+      <c r="L229" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M229" s="16" t="inlineStr">
+        <is>
+          <t>Plan flags stored-only — code/UI review</t>
+        </is>
+      </c>
+      <c r="N229" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O229" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -13882,6 +18543,26 @@
       <c r="K230" s="2" t="inlineStr">
         <is>
           <t>PG-464, FR-220</t>
+        </is>
+      </c>
+      <c r="L230" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M230" s="16" t="inlineStr">
+        <is>
+          <t>plans load without requiring Stripe price IDs</t>
+        </is>
+      </c>
+      <c r="N230" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:21.743Z</t>
+        </is>
+      </c>
+      <c r="O230" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -13943,6 +18624,26 @@
           <t>FR-223</t>
         </is>
       </c>
+      <c r="L231" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M231" s="16" t="inlineStr">
+        <is>
+          <t>New checkout pricing — Stripe</t>
+        </is>
+      </c>
+      <c r="N231" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O231" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -13998,6 +18699,26 @@
       <c r="K232" s="2" t="inlineStr">
         <is>
           <t>PG-470, FR-251</t>
+        </is>
+      </c>
+      <c r="L232" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M232" s="16" t="inlineStr">
+        <is>
+          <t>UI /super-admin/reports</t>
+        </is>
+      </c>
+      <c r="N232" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:23.345Z</t>
+        </is>
+      </c>
+      <c r="O232" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -14059,6 +18780,26 @@
           <t>PG-480, PG-481, NFR-100</t>
         </is>
       </c>
+      <c r="L233" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M233" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N233" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:24.786Z</t>
+        </is>
+      </c>
+      <c r="O233" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -14115,6 +18856,26 @@
       <c r="K234" s="2" t="inlineStr">
         <is>
           <t>NFR-100</t>
+        </is>
+      </c>
+      <c r="L234" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M234" s="16" t="inlineStr">
+        <is>
+          <t>Audit capture after action — needs write then check</t>
+        </is>
+      </c>
+      <c r="N234" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O234" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -14176,6 +18937,26 @@
           <t>PG-490</t>
         </is>
       </c>
+      <c r="L235" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M235" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N235" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:26.229Z</t>
+        </is>
+      </c>
+      <c r="O235" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -14235,6 +19016,26 @@
           <t>PG-491, PG-492, NFR-030</t>
         </is>
       </c>
+      <c r="L236" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M236" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N236" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O236" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -14290,6 +19091,26 @@
       <c r="K237" s="2" t="inlineStr">
         <is>
           <t>PG-493, PG-520</t>
+        </is>
+      </c>
+      <c r="L237" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M237" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N237" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O237" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -14351,6 +19172,26 @@
           <t>PG-494</t>
         </is>
       </c>
+      <c r="L238" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M238" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N238" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O238" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -14408,6 +19249,26 @@
           <t>PG-495</t>
         </is>
       </c>
+      <c r="L239" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M239" s="16" t="inlineStr">
+        <is>
+          <t>settings include stripeConfigured flag when present</t>
+        </is>
+      </c>
+      <c r="N239" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:22.666Z</t>
+        </is>
+      </c>
+      <c r="O239" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -14464,6 +19325,26 @@
       <c r="K240" s="2" t="inlineStr">
         <is>
           <t>PG-496, FR-256</t>
+        </is>
+      </c>
+      <c r="L240" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M240" s="16" t="inlineStr">
+        <is>
+          <t>tenant cannot hit platform APIs</t>
+        </is>
+      </c>
+      <c r="N240" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:19.518Z</t>
+        </is>
+      </c>
+      <c r="O240" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -14525,6 +19406,26 @@
           <t>PG-500</t>
         </is>
       </c>
+      <c r="L241" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M241" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N241" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:27.619Z</t>
+        </is>
+      </c>
+      <c r="O241" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -14583,6 +19484,26 @@
           <t>PG-501</t>
         </is>
       </c>
+      <c r="L242" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M242" s="16" t="inlineStr">
+        <is>
+          <t>status=200; UI ok</t>
+        </is>
+      </c>
+      <c r="N242" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.065Z</t>
+        </is>
+      </c>
+      <c r="O242" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -14641,6 +19562,26 @@
           <t>PG-001, FR-030-FR-037</t>
         </is>
       </c>
+      <c r="L243" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M243" s="16" t="inlineStr">
+        <is>
+          <t>admin nav renders role-filtered links</t>
+        </is>
+      </c>
+      <c r="N243" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:02.579Z</t>
+        </is>
+      </c>
+      <c r="O243" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -14698,6 +19639,26 @@
           <t>PG-002, NFR-215</t>
         </is>
       </c>
+      <c r="L244" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M244" s="16" t="inlineStr">
+        <is>
+          <t>dark mode toggle needs visual assertion</t>
+        </is>
+      </c>
+      <c r="N244" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.065Z</t>
+        </is>
+      </c>
+      <c r="O244" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -14756,6 +19717,26 @@
           <t>PG-003, FR-260</t>
         </is>
       </c>
+      <c r="L245" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M245" s="16" t="inlineStr">
+        <is>
+          <t>Ctrl+K backed by /api/search</t>
+        </is>
+      </c>
+      <c r="N245" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:16.407Z</t>
+        </is>
+      </c>
+      <c r="O245" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -14813,6 +19794,26 @@
           <t>PG-003, FR-260, FR-261</t>
         </is>
       </c>
+      <c r="L246" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M246" s="16" t="inlineStr">
+        <is>
+          <t>recently-viewed empty-search needs seeded recent views</t>
+        </is>
+      </c>
+      <c r="N246" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.065Z</t>
+        </is>
+      </c>
+      <c r="O246" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -14871,6 +19872,26 @@
           <t>PG-004</t>
         </is>
       </c>
+      <c r="L247" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M247" s="16" t="inlineStr">
+        <is>
+          <t>bell uses notifications API</t>
+        </is>
+      </c>
+      <c r="N247" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.065Z</t>
+        </is>
+      </c>
+      <c r="O247" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -14929,6 +19950,26 @@
           <t>PG-006, FR-019</t>
         </is>
       </c>
+      <c r="L248" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M248" s="16" t="inlineStr">
+        <is>
+          <t>logout revoke needs refresh-token DB check after UI logout</t>
+        </is>
+      </c>
+      <c r="N248" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.065Z</t>
+        </is>
+      </c>
+      <c r="O248" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -14987,6 +20028,26 @@
           <t>PG-008, NFR-110</t>
         </is>
       </c>
+      <c r="L249" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M249" s="16" t="inlineStr">
+        <is>
+          <t>unsaved guards need dirty-form interaction per page</t>
+        </is>
+      </c>
+      <c r="N249" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.065Z</t>
+        </is>
+      </c>
+      <c r="O249" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -15044,6 +20105,26 @@
           <t>CR-010, FR-050, FR-274</t>
         </is>
       </c>
+      <c r="L250" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M250" s="16" t="inlineStr">
+        <is>
+          <t>APIs use JWT company; no companyId accepted from body on reads</t>
+        </is>
+      </c>
+      <c r="N250" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:16.862Z</t>
+        </is>
+      </c>
+      <c r="O250" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -15101,6 +20182,26 @@
           <t>FR-051</t>
         </is>
       </c>
+      <c r="L251" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M251" s="16" t="inlineStr">
+        <is>
+          <t>status=404</t>
+        </is>
+      </c>
+      <c r="N251" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:16.862Z</t>
+        </is>
+      </c>
+      <c r="O251" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -15158,6 +20259,26 @@
           <t>FR-052, FR-055, NFR-070</t>
         </is>
       </c>
+      <c r="L252" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M252" s="16" t="inlineStr">
+        <is>
+          <t>RLS FORCE — DB-level; covered by 404 isolation smoke</t>
+        </is>
+      </c>
+      <c r="N252" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O252" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -15215,6 +20336,26 @@
           <t>FR-054</t>
         </is>
       </c>
+      <c r="L253" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M253" s="16" t="inlineStr">
+        <is>
+          <t>Needs suspended company fixture</t>
+        </is>
+      </c>
+      <c r="N253" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O253" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -15272,6 +20413,26 @@
           <t>FR-054</t>
         </is>
       </c>
+      <c r="L254" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M254" s="16" t="inlineStr">
+        <is>
+          <t>Needs expired-trial company fixture</t>
+        </is>
+      </c>
+      <c r="N254" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O254" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -15327,6 +20488,26 @@
       <c r="K255" s="2" t="inlineStr">
         <is>
           <t>FR-031</t>
+        </is>
+      </c>
+      <c r="L255" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M255" s="16" t="inlineStr">
+        <is>
+          <t>owner/office perms n=22</t>
+        </is>
+      </c>
+      <c r="N255" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.969Z</t>
+        </is>
+      </c>
+      <c r="O255" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -15388,6 +20569,26 @@
           <t>FR-032</t>
         </is>
       </c>
+      <c r="L256" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M256" s="16" t="inlineStr">
+        <is>
+          <t>Needs admin (non-owner) persona</t>
+        </is>
+      </c>
+      <c r="N256" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O256" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -15446,6 +20647,26 @@
           <t>FR-033</t>
         </is>
       </c>
+      <c r="L257" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M257" s="16" t="inlineStr">
+        <is>
+          <t>Needs dispatcher persona</t>
+        </is>
+      </c>
+      <c r="N257" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O257" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -15504,6 +20725,26 @@
           <t>FR-034</t>
         </is>
       </c>
+      <c r="L258" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M258" s="16" t="inlineStr">
+        <is>
+          <t>Needs office-role persona</t>
+        </is>
+      </c>
+      <c r="N258" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O258" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -15560,6 +20801,26 @@
       <c r="K259" s="2" t="inlineStr">
         <is>
           <t>FR-035, FR-244</t>
+        </is>
+      </c>
+      <c r="L259" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M259" s="16" t="inlineStr">
+        <is>
+          <t>field_worker session loads reduced permission set</t>
+        </is>
+      </c>
+      <c r="N259" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.969Z</t>
+        </is>
+      </c>
+      <c r="O259" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -15621,6 +20882,26 @@
           <t>FR-036</t>
         </is>
       </c>
+      <c r="L260" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M260" s="16" t="inlineStr">
+        <is>
+          <t>Mutating/deep flow — not auto-run on shared live DB; needs dedicated test tenant</t>
+        </is>
+      </c>
+      <c r="N260" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O260" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -15679,6 +20960,26 @@
           <t>FR-037</t>
         </is>
       </c>
+      <c r="L261" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M261" s="16" t="inlineStr">
+        <is>
+          <t>calendar/dispatch/inventory/reports gated by plan feature on API</t>
+        </is>
+      </c>
+      <c r="N261" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.969Z</t>
+        </is>
+      </c>
+      <c r="O261" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -15736,6 +21037,26 @@
           <t>FR-271, CR-070</t>
         </is>
       </c>
+      <c r="L262" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M262" s="16" t="inlineStr">
+        <is>
+          <t>Email channel architecture — code review</t>
+        </is>
+      </c>
+      <c r="N262" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O262" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -15793,6 +21114,26 @@
           <t>FR-271, PG-133, PG-136, PG-246</t>
         </is>
       </c>
+      <c r="L263" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M263" s="16" t="inlineStr">
+        <is>
+          <t>Email channel architecture — code review</t>
+        </is>
+      </c>
+      <c r="N263" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O263" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -15850,6 +21191,26 @@
           <t>FR-273</t>
         </is>
       </c>
+      <c r="L264" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M264" s="16" t="inlineStr">
+        <is>
+          <t>Email channel architecture — code review</t>
+        </is>
+      </c>
+      <c r="N264" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O264" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -15907,6 +21268,26 @@
           <t>PG-510 – PG-514</t>
         </is>
       </c>
+      <c r="L265" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M265" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N265" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O265" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -15964,6 +21345,26 @@
           <t>PG-515 – PG-519</t>
         </is>
       </c>
+      <c r="L266" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M266" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N266" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O266" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -16022,6 +21423,26 @@
           <t>NFR-030, FR-272</t>
         </is>
       </c>
+      <c r="L267" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M267" s="16" t="inlineStr">
+        <is>
+          <t>SMTP password fields not returned on company GET smoke</t>
+        </is>
+      </c>
+      <c r="N267" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.969Z</t>
+        </is>
+      </c>
+      <c r="O267" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -16080,6 +21501,26 @@
           <t>NFR-010</t>
         </is>
       </c>
+      <c r="L268" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M268" s="16" t="inlineStr">
+        <is>
+          <t>Auth uses argon2 verify in backend (code/review); login works with hashed passwords</t>
+        </is>
+      </c>
+      <c r="N268" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.968Z</t>
+        </is>
+      </c>
+      <c r="O268" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -16137,6 +21578,26 @@
           <t>NFR-020</t>
         </is>
       </c>
+      <c r="L269" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M269" s="16" t="inlineStr">
+        <is>
+          <t>refresh/reset tokens stored hashed (sha256) per auth routes</t>
+        </is>
+      </c>
+      <c r="N269" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.968Z</t>
+        </is>
+      </c>
+      <c r="O269" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -16194,6 +21655,26 @@
           <t>NFR-040</t>
         </is>
       </c>
+      <c r="L270" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M270" s="16" t="inlineStr">
+        <is>
+          <t>auth router has express-rate-limit 100/15m in code; not exhaustively load-tested</t>
+        </is>
+      </c>
+      <c r="N270" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.969Z</t>
+        </is>
+      </c>
+      <c r="O270" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -16252,6 +21733,26 @@
           <t>FR-017, FR-018</t>
         </is>
       </c>
+      <c r="L271" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M271" s="16" t="inlineStr">
+        <is>
+          <t>JWT_ACCESS_TTL=15m / refresh 14d configured in env (runtime uses signed tokens)</t>
+        </is>
+      </c>
+      <c r="N271" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.968Z</t>
+        </is>
+      </c>
+      <c r="O271" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -16310,6 +21811,26 @@
           <t>NFR-060</t>
         </is>
       </c>
+      <c r="L272" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M272" s="16" t="inlineStr">
+        <is>
+          <t>Production NODE_ENV rejects placeholder secrets (env.ts guard)</t>
+        </is>
+      </c>
+      <c r="N272" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.969Z</t>
+        </is>
+      </c>
+      <c r="O272" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -16367,6 +21888,26 @@
           <t>NFR-050</t>
         </is>
       </c>
+      <c r="L273" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M273" s="16" t="inlineStr">
+        <is>
+          <t>sample header present=true</t>
+        </is>
+      </c>
+      <c r="N273" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.968Z</t>
+        </is>
+      </c>
+      <c r="O273" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -16425,6 +21966,26 @@
           <t>FR-222, NFR-080</t>
         </is>
       </c>
+      <c r="L274" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M274" s="16" t="inlineStr">
+        <is>
+          <t>Stripe webhook idempotency — needs webhook events</t>
+        </is>
+      </c>
+      <c r="N274" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O274" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -16483,6 +22044,26 @@
           <t>NFR-090</t>
         </is>
       </c>
+      <c r="L275" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M275" s="16" t="inlineStr">
+        <is>
+          <t>FILE_DRIVER=local configured on Render</t>
+        </is>
+      </c>
+      <c r="N275" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.969Z</t>
+        </is>
+      </c>
+      <c r="O275" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -16541,6 +22122,26 @@
           <t>NFR-105</t>
         </is>
       </c>
+      <c r="L276" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M276" s="16" t="inlineStr">
+        <is>
+          <t>Requires outbound SMTP/Twilio delivery verification</t>
+        </is>
+      </c>
+      <c r="N276" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O276" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -16597,6 +22198,26 @@
       <c r="K277" s="2" t="inlineStr">
         <is>
           <t>NFR-120</t>
+        </is>
+      </c>
+      <c r="L277" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M277" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N277" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.170Z</t>
+        </is>
+      </c>
+      <c r="O277" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -16658,6 +22279,26 @@
           <t>NFR-130</t>
         </is>
       </c>
+      <c r="L278" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M278" s="16" t="inlineStr">
+        <is>
+          <t>list endpoints accept page/pageSize (tested jobs/customers)</t>
+        </is>
+      </c>
+      <c r="N278" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:19:23.969Z</t>
+        </is>
+      </c>
+      <c r="O278" s="16" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -16714,6 +22355,26 @@
       <c r="K279" s="2" t="inlineStr">
         <is>
           <t>NFR-140</t>
+        </is>
+      </c>
+      <c r="L279" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="M279" s="16" t="inlineStr">
+        <is>
+          <t>Manual multi-step UI verification required</t>
+        </is>
+      </c>
+      <c r="N279" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:20:29.171Z</t>
+        </is>
+      </c>
+      <c r="O279" s="16" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -16729,8 +22390,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F87"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -17379,6 +23040,194 @@
         <v>2</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>LIVE EXECUTION RESULTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FE: https://field-worker-system.vercel.app</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>API: https://fieldpro-backend-ulp9.onrender.com/api</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ran at: 2026-08-27T20:20:29.171Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="23" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Note: BLOCKED = mutating/email/Twilio/Stripe/multi-step cases not auto-run on shared live DB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Missing from runner map: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>LIVE EXECUTION RESULTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FE: https://field-worker-system.vercel.app</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>API: https://fieldpro-backend-ulp9.onrender.com/api</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ran at: 2026-08-27T20:20:29.171Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="22" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="23" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Note: BLOCKED = mutating/email/Twilio/Stripe/multi-step cases not auto-run on shared live DB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Missing from runner map: 0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
